--- a/ExcelFiles/wolfssl.xlsx
+++ b/ExcelFiles/wolfssl.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muyeedahmed/Desktop/Gitcode/LLMVerification/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D652B41F-94CF-7346-8048-7B6BD10A4A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F662CBB7-F5A9-9F40-81DB-613E71564C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10020" yWindow="4120" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="wolfssl" sheetId="1" r:id="rId1"/>
+    <sheet name="Commits" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
